--- a/testmanager.xlsx
+++ b/testmanager.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ExecutionPlan" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TestConfiguration" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ExecutionPlan" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="TestConfiguration" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="27.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -904,14 +904,43 @@
           <t>volunteering-teams</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Create_invoice_payables</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Create_invoice_payables</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>invoice_creation_3.xlsx</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>10005,10003</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Invoice ID</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
